--- a/ig/ch-vacd/StructureDefinition-ch-vacd-allergyintolerances.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-allergyintolerances.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1019,7 +1019,7 @@
     <t>certainty</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {allergyintolerance-certainty|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {allergyintolerance-certainty|5.3.0}
 </t>
   </si>
   <si>
@@ -1041,7 +1041,7 @@
     <t>duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {allergyintolerance-duration|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {allergyintolerance-duration|5.3.0}
 </t>
   </si>
   <si>
@@ -1057,7 +1057,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-location|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-location|5.3.0}
 </t>
   </si>
   <si>
@@ -1073,7 +1073,7 @@
     <t>exposureDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDate|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDate|5.3.0}
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
     <t>exposureDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDuration|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDuration|5.3.0}
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
     <t>exposureDescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDescription|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDescription|5.3.0}
 </t>
   </si>
   <si>
@@ -1124,7 +1124,7 @@
     <t>management</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-management|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-management|5.3.0}
 </t>
   </si>
   <si>
